--- a/Olympic_Kilns_2026_Pricelist.xlsx
+++ b/Olympic_Kilns_2026_Pricelist.xlsx
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1637" uniqueCount="639">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="646">
   <si>
     <t xml:space="preserve">Category</t>
   </si>
@@ -1875,7 +1875,10 @@
     <t xml:space="preserve">Olympic Kilns — 2026 Pricing (effective OCT 2026)</t>
   </si>
   <si>
-    <t xml:space="preserve">Source: 2026_New_Pricing_OCT26.xlsx, sheet "Sheet1" — all prices copied from that file, none calculated.</t>
+    <t xml:space="preserve">Source: 2026_New_Pricing_OCT26.xlsx, sheet "Sheet1". Prices are copied from that file, not calculated,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">except for the corrections listed below.</t>
   </si>
   <si>
     <t xml:space="preserve">Olympic Kilns, PO Box 1347, 4225 Thurmon Tanner Pkwy., Flowery Branch, GA 30542 — Sales (800) 241-4400 — olympickilns.com</t>
@@ -1908,31 +1911,49 @@
     <t xml:space="preserve">30% off), shown the same way: a base distributor price plus the distributor cost of each upgrade.</t>
   </si>
   <si>
+    <t xml:space="preserve">Corrections applied to the source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• 1818E / Genesis list price set to $2,925 as confirmed by Sheffield Pottery; the source sheet printed $2,425, which was out of line with the $150 Genesis upgrade every other model carries.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source figures that look wrong but were left as printed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• GF5E / KilnStar: distributor $3,240 is 72.0% of list $4,500; the usual 40% off would be $2,700 (source row 331)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• GF17E / Genesis: distributor $11,935 is 87.1% of list $13,700; the usual 30% off would be $9,590 (source row 595)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• GF17E CS / KilnStar: distributor $9,485 is 64.1% of list $14,800; the usual 30% off would be $10,360 (source row 594)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• GF17E CS / Genesis: distributor $25,550 is 170.9% of list $14,950; the usual 30% off would be $10,465 (source row 595)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Carried over from the source as printed</t>
   </si>
   <si>
-    <t xml:space="preserve">• GF17E / Genesis: distributor $11,935 is 87% of list $13,700 (source row 595)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• GF17E CS / Genesis: distributor $25,550 is 171% of list $14,950 (source row 595)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Three models come out with a NEGATIVE upgrade because that is how the source prices them: HB86 Vitrigraph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  (KilnStar $1,625 vs Spark $1,700), 1818E (Genesis $2,425 vs KilnStar $2,775) and DM2823HE (Genesis $5,835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  vs KilnStar $5,985). Every other model in those sections adds $125-$150 for Genesis, so 1818E and DM2823HE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  look like typos in the source sheet.</t>
+    <t xml:space="preserve">• 1818E / Genesis distributor price is still the source's $1,455, which was 40% off the old $2,425 list.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  40% off the corrected $2,925 list would be $1,755 — confirm with Olympic before quoting dealer cost.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  This is why the 1818E row shows a negative Genesis Upgrade D$.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Two models come out with a NEGATIVE upgrade because that is how the source prices them: HB86 Vitrigraph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  (KilnStar $1,625 vs Spark $1,700 — different controllers rather than tiers) and DM2823HE (Genesis $5,835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  vs KilnStar $5,985, where every other Dual Media model adds $150 for Genesis).</t>
   </si>
   <si>
     <t xml:space="preserve">• 2318HE and GF12E have no distributor price in the source.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• GF17E CS / KilnStar: the source repeats GF17E's distributor price ($9,485); 30% off list would be $10,360.</t>
   </si>
   <si>
     <t xml:space="preserve">• "GE12E CS" is spelled that way in the source (elsewhere GF12E CS).</t>
@@ -4009,7 +4030,7 @@
       </c>
       <c r="F48" s="3" t="n">
         <f aca="false">IF(OR($D48="",INDEX('Controller Prices'!$E:$E,MATCH($B48,'Controller Prices'!$B:$B,0))=""),"",INDEX('Controller Prices'!$E:$E,MATCH($B48,'Controller Prices'!$B:$B,0))-$D48)</f>
-        <v>-350</v>
+        <v>150</v>
       </c>
       <c r="G48" s="3" t="n">
         <v>1665</v>
@@ -10171,7 +10192,7 @@
         <v>2775</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>2425</v>
+        <v>2925</v>
       </c>
       <c r="F48" s="2"/>
       <c r="G48" s="2"/>
@@ -18039,7 +18060,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:A33"/>
+  <dimension ref="A1:A42"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="120"/>
@@ -18061,15 +18082,15 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="7"/>
+      <c r="A4" s="7" t="s">
+        <v>612</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="6" t="s">
-        <v>612</v>
-      </c>
+      <c r="A5" s="7"/>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>613</v>
       </c>
     </row>
@@ -18109,15 +18130,15 @@
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7"/>
+      <c r="A14" s="7" t="s">
+        <v>621</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="6" t="s">
-        <v>621</v>
-      </c>
+      <c r="A15" s="7"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="6" t="s">
         <v>622</v>
       </c>
     </row>
@@ -18127,81 +18148,122 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="7"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="6" t="s">
         <v>624</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>625</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
         <v>629</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="7" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="7" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
         <v>632</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>633</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="7" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="7" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="7" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="7" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="7" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="7" t="s">
         <v>638</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="7" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="7"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="6" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="7" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="7" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="7" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="7" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="7" t="s">
+        <v>645</v>
       </c>
     </row>
   </sheetData>
